--- a/research/traditional_assets/database/data/denmark/denmark_retail_online.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_retail_online.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09269999999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="G2">
-        <v>-0.02891402714932126</v>
+        <v>0.005838509316770184</v>
       </c>
       <c r="H2">
-        <v>-0.1297285067873303</v>
+        <v>-0.04857142857142857</v>
       </c>
       <c r="I2">
-        <v>-0.07457013574660634</v>
+        <v>-0.00484472049689441</v>
       </c>
       <c r="J2">
-        <v>-0.07457013574660634</v>
+        <v>-0.00484472049689441</v>
       </c>
       <c r="K2">
-        <v>-6.563000000000001</v>
+        <v>-2.63</v>
       </c>
       <c r="L2">
-        <v>-0.2969683257918552</v>
+        <v>-0.1633540372670807</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.88</v>
+        <v>0.313</v>
       </c>
       <c r="V2">
-        <v>0.5834586466165413</v>
+        <v>0.2524193548387097</v>
       </c>
       <c r="W2">
-        <v>1.857326113483832</v>
+        <v>0.4221508828250401</v>
       </c>
       <c r="X2">
-        <v>0.2157168266088535</v>
+        <v>0.8776842852284521</v>
       </c>
       <c r="Y2">
-        <v>1.641609286874978</v>
+        <v>-0.455533402403412</v>
       </c>
       <c r="Z2">
-        <v>2.585702585702584</v>
+        <v>4.86404833836858</v>
       </c>
       <c r="AA2">
-        <v>-0.2720801559795488</v>
+        <v>-0.02356495468277945</v>
       </c>
       <c r="AB2">
-        <v>0.06804791009784852</v>
+        <v>0.113126086409992</v>
       </c>
       <c r="AC2">
-        <v>-0.3401280660773973</v>
+        <v>-0.1366910410927714</v>
       </c>
       <c r="AD2">
-        <v>20.09</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.09</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>16.21</v>
+        <v>13.187</v>
       </c>
       <c r="AH2">
-        <v>0.7513089005235601</v>
+        <v>0.9158751696065128</v>
       </c>
       <c r="AI2">
-        <v>1.263522012578616</v>
+        <v>1.807228915662651</v>
       </c>
       <c r="AJ2">
-        <v>0.7090988626421698</v>
+        <v>0.9140500450544119</v>
       </c>
       <c r="AK2">
-        <v>1.348585690515807</v>
+        <v>1.842531787061618</v>
       </c>
       <c r="AL2">
-        <v>1.37</v>
+        <v>0.757</v>
       </c>
       <c r="AM2">
-        <v>1.162</v>
+        <v>0.612</v>
       </c>
       <c r="AN2">
-        <v>-8.823012736056214</v>
+        <v>-24.63503649635036</v>
       </c>
       <c r="AO2">
-        <v>-1.202919708029197</v>
+        <v>-0.1030383091149273</v>
       </c>
       <c r="AP2">
-        <v>-7.119016249451032</v>
+        <v>-24.06386861313868</v>
       </c>
       <c r="AQ2">
-        <v>-1.418244406196213</v>
+        <v>-0.1274509803921569</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.09269999999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="G3">
-        <v>-0.02644230769230768</v>
+        <v>0.005838509316770184</v>
       </c>
       <c r="H3">
-        <v>-0.1024038461538462</v>
+        <v>-0.04857142857142857</v>
       </c>
       <c r="I3">
-        <v>-0.04192307692307692</v>
+        <v>-0.00484472049689441</v>
       </c>
       <c r="J3">
-        <v>-0.04192307692307692</v>
+        <v>-0.00484472049689441</v>
       </c>
       <c r="K3">
-        <v>-5.95</v>
+        <v>-2.63</v>
       </c>
       <c r="L3">
-        <v>-0.2860576923076923</v>
+        <v>-0.1633540372670807</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,198 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.74</v>
+        <v>0.313</v>
       </c>
       <c r="V3">
-        <v>0.9102990033222593</v>
+        <v>0.2524193548387097</v>
       </c>
       <c r="W3">
-        <v>3.993288590604027</v>
+        <v>0.4221508828250401</v>
       </c>
       <c r="X3">
-        <v>0.3421880349325722</v>
+        <v>0.8776842852284521</v>
       </c>
       <c r="Y3">
-        <v>3.651100555671455</v>
+        <v>-0.455533402403412</v>
       </c>
       <c r="Z3">
-        <v>3.118440779610193</v>
+        <v>4.86404833836858</v>
       </c>
       <c r="AA3">
-        <v>-0.1307346326836581</v>
+        <v>-0.02356495468277945</v>
       </c>
       <c r="AB3">
-        <v>0.06643622238845598</v>
+        <v>0.113126086409992</v>
       </c>
       <c r="AC3">
-        <v>-0.197170855072114</v>
+        <v>-0.1366910410927714</v>
       </c>
       <c r="AD3">
-        <v>18.6</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.6</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>15.86</v>
+        <v>13.187</v>
       </c>
       <c r="AH3">
-        <v>0.8607126330402592</v>
+        <v>0.9158751696065128</v>
       </c>
       <c r="AI3">
-        <v>1.503637833468068</v>
+        <v>1.807228915662651</v>
       </c>
       <c r="AJ3">
-        <v>0.8404875463698993</v>
+        <v>0.9140500450544119</v>
       </c>
       <c r="AK3">
-        <v>1.646936656282451</v>
+        <v>1.842531787061618</v>
       </c>
       <c r="AL3">
-        <v>1.27</v>
+        <v>0.757</v>
       </c>
       <c r="AM3">
-        <v>1.062</v>
+        <v>0.612</v>
       </c>
       <c r="AN3">
-        <v>-12.07792207792208</v>
+        <v>-24.63503649635036</v>
       </c>
       <c r="AO3">
-        <v>-0.6866141732283464</v>
+        <v>-0.1030383091149273</v>
       </c>
       <c r="AP3">
-        <v>-10.2987012987013</v>
+        <v>-24.06386861313868</v>
       </c>
       <c r="AQ3">
-        <v>-0.8210922787193973</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Happy Helper A/S (CPSE:HAPPY)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Retail (Online)</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-0.06846153846153843</v>
-      </c>
-      <c r="H4">
-        <v>-0.5669230769230769</v>
-      </c>
-      <c r="I4">
-        <v>-0.5969230769230769</v>
-      </c>
-      <c r="J4">
-        <v>-0.5969230769230769</v>
-      </c>
-      <c r="K4">
-        <v>-0.613</v>
-      </c>
-      <c r="L4">
-        <v>-0.4715384615384615</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1.14</v>
-      </c>
-      <c r="V4">
-        <v>0.3131868131868131</v>
-      </c>
-      <c r="W4">
-        <v>-0.2786363636363636</v>
-      </c>
-      <c r="X4">
-        <v>0.08924561828513476</v>
-      </c>
-      <c r="Y4">
-        <v>-0.3678819819214984</v>
-      </c>
-      <c r="Z4">
-        <v>0.6925945657964837</v>
-      </c>
-      <c r="AA4">
-        <v>-0.4134256792754395</v>
-      </c>
-      <c r="AB4">
-        <v>0.06965959780724106</v>
-      </c>
-      <c r="AC4">
-        <v>-0.4830852770826806</v>
-      </c>
-      <c r="AD4">
-        <v>1.49</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1.49</v>
-      </c>
-      <c r="AG4">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.290448343079922</v>
-      </c>
-      <c r="AI4">
-        <v>0.4220963172804532</v>
-      </c>
-      <c r="AJ4">
-        <v>0.08771929824561406</v>
-      </c>
-      <c r="AK4">
-        <v>0.1464435146443515</v>
-      </c>
-      <c r="AL4">
-        <v>0.1</v>
-      </c>
-      <c r="AM4">
-        <v>0.1</v>
-      </c>
-      <c r="AN4">
-        <v>-2.021709633649932</v>
-      </c>
-      <c r="AO4">
-        <v>-7.76</v>
-      </c>
-      <c r="AP4">
-        <v>-0.4748982360922661</v>
-      </c>
-      <c r="AQ4">
-        <v>-7.76</v>
+        <v>-0.1274509803921569</v>
       </c>
     </row>
   </sheetData>
